--- a/sw-work/skills/auto-created-table/autoCreateTable.xlsx
+++ b/sw-work/skills/auto-created-table/autoCreateTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>岗位交班</t>
   </si>
@@ -98,7 +98,7 @@
     <t>是否执行成功（0-否 1-是）</t>
   </si>
   <si>
-    <t>varchar(1)</t>
+    <t>varchar(36)</t>
   </si>
   <si>
     <t>executedResult</t>
@@ -108,24 +108,6 @@
   </si>
   <si>
     <t>varchar(300)</t>
-  </si>
-  <si>
-    <t>log</t>
-  </si>
-  <si>
-    <t>日志</t>
-  </si>
-  <si>
-    <t>longtext</t>
-  </si>
-  <si>
-    <t>orderId</t>
-  </si>
-  <si>
-    <t>样品编码</t>
-  </si>
-  <si>
-    <t>varchar(900)</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1153,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.5555555555556" customWidth="1"/>
@@ -1304,37 +1286,11 @@
       <c r="E10" s="8"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1"/>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="9">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D4:F4"/>
@@ -1344,8 +1300,6 @@
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
